--- a/5. SMS Reports/.Reports/12. Dec/SMS-Crystal Lake 12.31.25 Financial Report_Final.xlsx
+++ b/5. SMS Reports/.Reports/12. Dec/SMS-Crystal Lake 12.31.25 Financial Report_Final.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General Ledger" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12 Month Statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="mm-yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm-yyyy"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -195,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -227,7 +226,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -392,6 +391,9 @@
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,7 +906,7 @@
       <c r="C8" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -947,7 +949,7 @@
       <c r="C9" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
@@ -990,7 +992,7 @@
       <c r="C10" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -1037,7 +1039,7 @@
       <c r="C11" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E11" s="9" t="inlineStr">
@@ -1080,7 +1082,7 @@
       <c r="C12" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E12" s="9" t="inlineStr">
@@ -1127,7 +1129,7 @@
       <c r="C13" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -1174,7 +1176,7 @@
       <c r="C14" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D14" s="11" t="n">
+      <c r="D14" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E14" s="9" t="inlineStr">
@@ -1221,7 +1223,7 @@
       <c r="C15" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E15" s="9" t="inlineStr">
@@ -1268,7 +1270,7 @@
       <c r="C16" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D16" s="11" t="n">
+      <c r="D16" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E16" s="9" t="inlineStr">
@@ -1311,7 +1313,7 @@
       <c r="C17" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D17" s="11" t="n">
+      <c r="D17" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E17" s="9" t="inlineStr">
@@ -1358,7 +1360,7 @@
       <c r="C18" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E18" s="9" t="inlineStr">
@@ -1405,7 +1407,7 @@
       <c r="C19" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E19" s="9" t="inlineStr">
@@ -1448,7 +1450,7 @@
       <c r="C20" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D20" s="11" t="n">
+      <c r="D20" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E20" s="9" t="inlineStr">
@@ -1491,7 +1493,7 @@
       <c r="C21" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E21" s="9" t="inlineStr">
@@ -1534,7 +1536,7 @@
       <c r="C22" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E22" s="9" t="inlineStr">
@@ -1577,7 +1579,7 @@
       <c r="C23" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D23" s="11" t="n">
+      <c r="D23" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E23" s="9" t="inlineStr">
@@ -1624,7 +1626,7 @@
       <c r="C24" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D24" s="11" t="n">
+      <c r="D24" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E24" s="9" t="inlineStr">
@@ -1667,7 +1669,7 @@
       <c r="C25" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E25" s="9" t="inlineStr">
@@ -1710,7 +1712,7 @@
       <c r="C26" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D26" s="11" t="n">
+      <c r="D26" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E26" s="9" t="inlineStr">
@@ -1753,7 +1755,7 @@
       <c r="C27" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D27" s="11" t="n">
+      <c r="D27" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -1796,7 +1798,7 @@
       <c r="C28" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D28" s="11" t="n">
+      <c r="D28" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E28" s="9" t="inlineStr">
@@ -1843,7 +1845,7 @@
       <c r="C29" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E29" s="9" t="inlineStr">
@@ -1886,7 +1888,7 @@
       <c r="C30" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D30" s="11" t="n">
+      <c r="D30" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E30" s="9" t="inlineStr">
@@ -1929,7 +1931,7 @@
       <c r="C31" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D31" s="11" t="n">
+      <c r="D31" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1976,7 +1978,7 @@
       <c r="C32" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E32" s="9" t="inlineStr">
@@ -2023,7 +2025,7 @@
       <c r="C33" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D33" s="11" t="n">
+      <c r="D33" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E33" s="9" t="inlineStr">
@@ -2070,7 +2072,7 @@
       <c r="C34" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E34" s="9" t="inlineStr">
@@ -2117,7 +2119,7 @@
       <c r="C35" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E35" s="9" t="inlineStr">
@@ -2164,7 +2166,7 @@
       <c r="C36" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E36" s="9" t="inlineStr">
@@ -2211,7 +2213,7 @@
       <c r="C37" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E37" s="9" t="inlineStr">
@@ -2258,7 +2260,7 @@
       <c r="C38" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D38" s="11" t="n">
+      <c r="D38" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E38" s="9" t="inlineStr">
@@ -2305,7 +2307,7 @@
       <c r="C39" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -2352,7 +2354,7 @@
       <c r="C40" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D40" s="11" t="n">
+      <c r="D40" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E40" s="9" t="inlineStr">
@@ -2399,7 +2401,7 @@
       <c r="C41" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D41" s="11" t="n">
+      <c r="D41" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -2446,7 +2448,7 @@
       <c r="C42" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -2493,7 +2495,7 @@
       <c r="C43" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -2540,7 +2542,7 @@
       <c r="C44" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D44" s="11" t="n">
+      <c r="D44" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E44" s="9" t="inlineStr">
@@ -2587,7 +2589,7 @@
       <c r="C45" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D45" s="11" t="n">
+      <c r="D45" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -2634,7 +2636,7 @@
       <c r="C46" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E46" s="9" t="inlineStr">
@@ -2681,7 +2683,7 @@
       <c r="C47" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D47" s="11" t="n">
+      <c r="D47" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -2728,7 +2730,7 @@
       <c r="C48" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D48" s="11" t="n">
+      <c r="D48" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E48" s="9" t="inlineStr">
@@ -2775,7 +2777,7 @@
       <c r="C49" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D49" s="11" t="n">
+      <c r="D49" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -2818,7 +2820,7 @@
       <c r="C50" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -2861,7 +2863,7 @@
       <c r="C51" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D51" s="11" t="n">
+      <c r="D51" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -2908,7 +2910,7 @@
       <c r="C52" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D52" s="11" t="n">
+      <c r="D52" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E52" s="9" t="inlineStr">
@@ -2955,7 +2957,7 @@
       <c r="C53" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E53" s="9" t="inlineStr">
@@ -2998,7 +3000,7 @@
       <c r="C54" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D54" s="11" t="n">
+      <c r="D54" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E54" s="9" t="inlineStr">
@@ -3041,7 +3043,7 @@
       <c r="C55" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D55" s="11" t="n">
+      <c r="D55" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E55" s="9" t="inlineStr">
@@ -3084,7 +3086,7 @@
       <c r="C56" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D56" s="11" t="n">
+      <c r="D56" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -3127,7 +3129,7 @@
       <c r="C57" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E57" s="9" t="inlineStr">
@@ -3170,7 +3172,7 @@
       <c r="C58" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D58" s="11" t="n">
+      <c r="D58" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -3213,7 +3215,7 @@
       <c r="C59" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D59" s="11" t="n">
+      <c r="D59" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -3260,7 +3262,7 @@
       <c r="C60" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -3303,7 +3305,7 @@
       <c r="C61" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D61" s="11" t="n">
+      <c r="D61" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -3350,7 +3352,7 @@
       <c r="C62" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D62" s="11" t="n">
+      <c r="D62" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -3397,7 +3399,7 @@
       <c r="C63" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D63" s="11" t="n">
+      <c r="D63" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -3511,7 +3513,7 @@
       <c r="C67" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D67" s="11" t="n">
+      <c r="D67" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E67" s="9" t="inlineStr">
@@ -3554,7 +3556,7 @@
       <c r="C68" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D68" s="11" t="n">
+      <c r="D68" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E68" s="9" t="inlineStr">
@@ -3597,7 +3599,7 @@
       <c r="C69" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D69" s="11" t="n">
+      <c r="D69" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E69" s="9" t="inlineStr">
@@ -3640,7 +3642,7 @@
       <c r="C70" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D70" s="11" t="n">
+      <c r="D70" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E70" s="9" t="inlineStr">
@@ -3683,7 +3685,7 @@
       <c r="C71" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D71" s="11" t="n">
+      <c r="D71" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E71" s="9" t="inlineStr">
@@ -3726,7 +3728,7 @@
       <c r="C72" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D72" s="11" t="n">
+      <c r="D72" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E72" s="9" t="inlineStr">
@@ -3769,7 +3771,7 @@
       <c r="C73" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D73" s="11" t="n">
+      <c r="D73" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E73" s="9" t="inlineStr">
@@ -3812,7 +3814,7 @@
       <c r="C74" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D74" s="11" t="n">
+      <c r="D74" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E74" s="9" t="inlineStr">
@@ -3855,7 +3857,7 @@
       <c r="C75" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D75" s="11" t="n">
+      <c r="D75" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E75" s="9" t="inlineStr">
@@ -3898,7 +3900,7 @@
       <c r="C76" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D76" s="11" t="n">
+      <c r="D76" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E76" s="9" t="inlineStr">
@@ -3941,7 +3943,7 @@
       <c r="C77" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D77" s="11" t="n">
+      <c r="D77" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E77" s="9" t="inlineStr">
@@ -3984,7 +3986,7 @@
       <c r="C78" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D78" s="11" t="n">
+      <c r="D78" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E78" s="9" t="inlineStr">
@@ -4027,7 +4029,7 @@
       <c r="C79" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D79" s="11" t="n">
+      <c r="D79" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E79" s="9" t="inlineStr">
@@ -4070,7 +4072,7 @@
       <c r="C80" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D80" s="11" t="n">
+      <c r="D80" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E80" s="9" t="inlineStr">
@@ -4113,7 +4115,7 @@
       <c r="C81" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D81" s="11" t="n">
+      <c r="D81" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E81" s="9" t="inlineStr">
@@ -4227,7 +4229,7 @@
       <c r="C85" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D85" s="11" t="n">
+      <c r="D85" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E85" s="9" t="inlineStr">
@@ -4558,7 +4560,7 @@
       <c r="C98" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D98" s="11" t="n">
+      <c r="D98" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E98" s="9" t="inlineStr">
@@ -4743,7 +4745,7 @@
       <c r="C105" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D105" s="11" t="n">
+      <c r="D105" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E105" s="9" t="inlineStr">
@@ -4790,7 +4792,7 @@
       <c r="C106" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D106" s="11" t="n">
+      <c r="D106" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E106" s="9" t="inlineStr">
@@ -4837,7 +4839,7 @@
       <c r="C107" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D107" s="11" t="n">
+      <c r="D107" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E107" s="9" t="inlineStr">
@@ -4884,7 +4886,7 @@
       <c r="C108" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D108" s="11" t="n">
+      <c r="D108" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E108" s="9" t="inlineStr">
@@ -4931,7 +4933,7 @@
       <c r="C109" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D109" s="11" t="n">
+      <c r="D109" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E109" s="9" t="inlineStr">
@@ -4978,7 +4980,7 @@
       <c r="C110" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D110" s="11" t="n">
+      <c r="D110" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E110" s="9" t="inlineStr">
@@ -5025,7 +5027,7 @@
       <c r="C111" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D111" s="11" t="n">
+      <c r="D111" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E111" s="9" t="inlineStr">
@@ -5072,7 +5074,7 @@
       <c r="C112" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D112" s="11" t="n">
+      <c r="D112" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E112" s="9" t="inlineStr">
@@ -5119,7 +5121,7 @@
       <c r="C113" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D113" s="11" t="n">
+      <c r="D113" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E113" s="9" t="inlineStr">
@@ -5166,7 +5168,7 @@
       <c r="C114" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D114" s="11" t="n">
+      <c r="D114" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E114" s="9" t="inlineStr">
@@ -5213,7 +5215,7 @@
       <c r="C115" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D115" s="11" t="n">
+      <c r="D115" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E115" s="9" t="inlineStr">
@@ -5260,7 +5262,7 @@
       <c r="C116" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D116" s="11" t="n">
+      <c r="D116" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E116" s="9" t="inlineStr">
@@ -5307,7 +5309,7 @@
       <c r="C117" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D117" s="11" t="n">
+      <c r="D117" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E117" s="9" t="inlineStr">
@@ -5354,7 +5356,7 @@
       <c r="C118" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D118" s="11" t="n">
+      <c r="D118" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E118" s="9" t="inlineStr">
@@ -5401,7 +5403,7 @@
       <c r="C119" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D119" s="11" t="n">
+      <c r="D119" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E119" s="9" t="inlineStr">
@@ -5448,7 +5450,7 @@
       <c r="C120" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D120" s="11" t="n">
+      <c r="D120" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E120" s="9" t="inlineStr">
@@ -5495,7 +5497,7 @@
       <c r="C121" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D121" s="11" t="n">
+      <c r="D121" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E121" s="9" t="inlineStr">
@@ -5542,7 +5544,7 @@
       <c r="C122" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D122" s="11" t="n">
+      <c r="D122" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E122" s="9" t="inlineStr">
@@ -5589,7 +5591,7 @@
       <c r="C123" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D123" s="11" t="n">
+      <c r="D123" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E123" s="9" t="inlineStr">
@@ -5636,7 +5638,7 @@
       <c r="C124" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D124" s="11" t="n">
+      <c r="D124" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E124" s="9" t="inlineStr">
@@ -5683,7 +5685,7 @@
       <c r="C125" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D125" s="11" t="n">
+      <c r="D125" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E125" s="9" t="inlineStr">
@@ -5730,7 +5732,7 @@
       <c r="C126" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D126" s="11" t="n">
+      <c r="D126" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -5777,7 +5779,7 @@
       <c r="C127" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D127" s="11" t="n">
+      <c r="D127" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -5824,7 +5826,7 @@
       <c r="C128" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D128" s="11" t="n">
+      <c r="D128" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E128" s="9" t="inlineStr">
@@ -5871,7 +5873,7 @@
       <c r="C129" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D129" s="11" t="n">
+      <c r="D129" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -5918,7 +5920,7 @@
       <c r="C130" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D130" s="11" t="n">
+      <c r="D130" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -5965,7 +5967,7 @@
       <c r="C131" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D131" s="11" t="n">
+      <c r="D131" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -6012,7 +6014,7 @@
       <c r="C132" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D132" s="11" t="n">
+      <c r="D132" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -6059,7 +6061,7 @@
       <c r="C133" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D133" s="11" t="n">
+      <c r="D133" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -6106,7 +6108,7 @@
       <c r="C134" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D134" s="11" t="n">
+      <c r="D134" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -6153,7 +6155,7 @@
       <c r="C135" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D135" s="11" t="n">
+      <c r="D135" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -6200,7 +6202,7 @@
       <c r="C136" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D136" s="11" t="n">
+      <c r="D136" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E136" s="9" t="inlineStr">
@@ -6247,7 +6249,7 @@
       <c r="C137" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D137" s="11" t="n">
+      <c r="D137" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -6294,7 +6296,7 @@
       <c r="C138" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D138" s="11" t="n">
+      <c r="D138" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -6341,7 +6343,7 @@
       <c r="C139" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D139" s="11" t="n">
+      <c r="D139" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E139" s="9" t="inlineStr">
@@ -6388,7 +6390,7 @@
       <c r="C140" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D140" s="11" t="n">
+      <c r="D140" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -6435,7 +6437,7 @@
       <c r="C141" s="10" t="n">
         <v>46003</v>
       </c>
-      <c r="D141" s="11" t="n">
+      <c r="D141" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E141" s="9" t="inlineStr">
@@ -6482,7 +6484,7 @@
       <c r="C142" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D142" s="11" t="n">
+      <c r="D142" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -6529,7 +6531,7 @@
       <c r="C143" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D143" s="11" t="n">
+      <c r="D143" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E143" s="9" t="inlineStr">
@@ -6576,7 +6578,7 @@
       <c r="C144" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D144" s="11" t="n">
+      <c r="D144" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -6623,7 +6625,7 @@
       <c r="C145" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D145" s="11" t="n">
+      <c r="D145" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -6670,7 +6672,7 @@
       <c r="C146" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D146" s="11" t="n">
+      <c r="D146" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -6717,7 +6719,7 @@
       <c r="C147" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D147" s="11" t="n">
+      <c r="D147" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E147" s="9" t="inlineStr">
@@ -6764,7 +6766,7 @@
       <c r="C148" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D148" s="11" t="n">
+      <c r="D148" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E148" s="9" t="inlineStr">
@@ -6811,7 +6813,7 @@
       <c r="C149" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D149" s="11" t="n">
+      <c r="D149" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E149" s="9" t="inlineStr">
@@ -6858,7 +6860,7 @@
       <c r="C150" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D150" s="11" t="n">
+      <c r="D150" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E150" s="9" t="inlineStr">
@@ -6905,7 +6907,7 @@
       <c r="C151" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D151" s="11" t="n">
+      <c r="D151" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E151" s="9" t="inlineStr">
@@ -6952,7 +6954,7 @@
       <c r="C152" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D152" s="11" t="n">
+      <c r="D152" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E152" s="9" t="inlineStr">
@@ -6999,7 +7001,7 @@
       <c r="C153" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D153" s="11" t="n">
+      <c r="D153" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E153" s="9" t="inlineStr">
@@ -7046,7 +7048,7 @@
       <c r="C154" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D154" s="11" t="n">
+      <c r="D154" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E154" s="9" t="inlineStr">
@@ -7093,7 +7095,7 @@
       <c r="C155" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D155" s="11" t="n">
+      <c r="D155" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E155" s="9" t="inlineStr">
@@ -7140,7 +7142,7 @@
       <c r="C156" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D156" s="11" t="n">
+      <c r="D156" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E156" s="9" t="inlineStr">
@@ -7187,7 +7189,7 @@
       <c r="C157" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D157" s="11" t="n">
+      <c r="D157" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E157" s="9" t="inlineStr">
@@ -7234,7 +7236,7 @@
       <c r="C158" s="10" t="n">
         <v>46023</v>
       </c>
-      <c r="D158" s="11" t="n">
+      <c r="D158" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E158" s="9" t="inlineStr">
@@ -7281,7 +7283,7 @@
       <c r="C159" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D159" s="11" t="n">
+      <c r="D159" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E159" s="9" t="inlineStr">
@@ -7328,7 +7330,7 @@
       <c r="C160" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D160" s="11" t="n">
+      <c r="D160" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E160" s="9" t="inlineStr">
@@ -7375,7 +7377,7 @@
       <c r="C161" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D161" s="11" t="n">
+      <c r="D161" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E161" s="9" t="inlineStr">
@@ -7422,7 +7424,7 @@
       <c r="C162" s="10" t="n">
         <v>46054</v>
       </c>
-      <c r="D162" s="11" t="n">
+      <c r="D162" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E162" s="9" t="inlineStr">
@@ -7540,7 +7542,7 @@
       <c r="C166" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D166" s="11" t="n">
+      <c r="D166" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E166" s="9" t="inlineStr">
@@ -7583,7 +7585,7 @@
       <c r="C167" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D167" s="11" t="n">
+      <c r="D167" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E167" s="9" t="inlineStr">
@@ -7626,7 +7628,7 @@
       <c r="C168" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D168" s="11" t="n">
+      <c r="D168" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E168" s="9" t="inlineStr">
@@ -7669,7 +7671,7 @@
       <c r="C169" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D169" s="11" t="n">
+      <c r="D169" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E169" s="9" t="inlineStr">
@@ -7712,7 +7714,7 @@
       <c r="C170" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D170" s="11" t="n">
+      <c r="D170" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E170" s="9" t="inlineStr">
@@ -7755,7 +7757,7 @@
       <c r="C171" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D171" s="11" t="n">
+      <c r="D171" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E171" s="9" t="inlineStr">
@@ -8011,7 +8013,7 @@
       <c r="C181" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D181" s="11" t="n">
+      <c r="D181" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E181" s="9" t="inlineStr">
@@ -8129,7 +8131,7 @@
       <c r="C185" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D185" s="11" t="n">
+      <c r="D185" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E185" s="9" t="inlineStr">
@@ -8172,7 +8174,7 @@
       <c r="C186" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D186" s="11" t="n">
+      <c r="D186" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E186" s="9" t="inlineStr">
@@ -8215,7 +8217,7 @@
       <c r="C187" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D187" s="11" t="n">
+      <c r="D187" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E187" s="9" t="inlineStr">
@@ -8258,7 +8260,7 @@
       <c r="C188" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D188" s="11" t="n">
+      <c r="D188" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E188" s="9" t="inlineStr">
@@ -8301,7 +8303,7 @@
       <c r="C189" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D189" s="11" t="n">
+      <c r="D189" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E189" s="9" t="inlineStr">
@@ -8344,7 +8346,7 @@
       <c r="C190" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D190" s="11" t="n">
+      <c r="D190" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E190" s="9" t="inlineStr">
@@ -8529,7 +8531,7 @@
       <c r="C197" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D197" s="11" t="n">
+      <c r="D197" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E197" s="9" t="inlineStr">
@@ -8572,7 +8574,7 @@
       <c r="C198" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D198" s="11" t="n">
+      <c r="D198" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E198" s="9" t="inlineStr">
@@ -8619,7 +8621,7 @@
       <c r="C199" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D199" s="11" t="n">
+      <c r="D199" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E199" s="9" t="inlineStr">
@@ -8662,7 +8664,7 @@
       <c r="C200" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D200" s="11" t="n">
+      <c r="D200" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E200" s="9" t="inlineStr">
@@ -8709,7 +8711,7 @@
       <c r="C201" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D201" s="11" t="n">
+      <c r="D201" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E201" s="9" t="inlineStr">
@@ -8752,7 +8754,7 @@
       <c r="C202" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D202" s="11" t="n">
+      <c r="D202" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E202" s="9" t="inlineStr">
@@ -8866,7 +8868,7 @@
       <c r="C206" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D206" s="11" t="n">
+      <c r="D206" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E206" s="9" t="inlineStr">
@@ -9193,7 +9195,7 @@
       <c r="C219" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D219" s="11" t="n">
+      <c r="D219" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E219" s="9" t="inlineStr">
@@ -9236,7 +9238,7 @@
       <c r="C220" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D220" s="11" t="n">
+      <c r="D220" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E220" s="9" t="inlineStr">
@@ -9279,7 +9281,7 @@
       <c r="C221" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D221" s="11" t="n">
+      <c r="D221" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E221" s="9" t="inlineStr">
@@ -9322,7 +9324,7 @@
       <c r="C222" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D222" s="11" t="n">
+      <c r="D222" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E222" s="9" t="inlineStr">
@@ -9365,7 +9367,7 @@
       <c r="C223" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D223" s="11" t="n">
+      <c r="D223" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E223" s="9" t="inlineStr">
@@ -9408,7 +9410,7 @@
       <c r="C224" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D224" s="11" t="n">
+      <c r="D224" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E224" s="9" t="inlineStr">
@@ -9451,7 +9453,7 @@
       <c r="C225" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D225" s="11" t="n">
+      <c r="D225" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E225" s="9" t="inlineStr">
@@ -9494,7 +9496,7 @@
       <c r="C226" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D226" s="11" t="n">
+      <c r="D226" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E226" s="9" t="inlineStr">
@@ -9537,7 +9539,7 @@
       <c r="C227" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D227" s="11" t="n">
+      <c r="D227" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E227" s="9" t="inlineStr">
@@ -9580,7 +9582,7 @@
       <c r="C228" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D228" s="11" t="n">
+      <c r="D228" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E228" s="9" t="inlineStr">
@@ -9623,7 +9625,7 @@
       <c r="C229" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D229" s="11" t="n">
+      <c r="D229" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E229" s="9" t="inlineStr">
@@ -9666,7 +9668,7 @@
       <c r="C230" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D230" s="11" t="n">
+      <c r="D230" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E230" s="9" t="inlineStr">
@@ -9709,7 +9711,7 @@
       <c r="C231" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D231" s="11" t="n">
+      <c r="D231" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E231" s="9" t="inlineStr">
@@ -9752,7 +9754,7 @@
       <c r="C232" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D232" s="11" t="n">
+      <c r="D232" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E232" s="9" t="inlineStr">
@@ -9795,7 +9797,7 @@
       <c r="C233" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D233" s="11" t="n">
+      <c r="D233" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E233" s="9" t="inlineStr">
@@ -9838,7 +9840,7 @@
       <c r="C234" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D234" s="11" t="n">
+      <c r="D234" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E234" s="9" t="inlineStr">
@@ -9881,7 +9883,7 @@
       <c r="C235" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D235" s="11" t="n">
+      <c r="D235" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E235" s="9" t="inlineStr">
@@ -9924,7 +9926,7 @@
       <c r="C236" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D236" s="11" t="n">
+      <c r="D236" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E236" s="9" t="inlineStr">
@@ -10038,7 +10040,7 @@
       <c r="C240" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D240" s="11" t="n">
+      <c r="D240" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E240" s="9" t="inlineStr">
@@ -10152,7 +10154,7 @@
       <c r="C244" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D244" s="11" t="n">
+      <c r="D244" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E244" s="9" t="inlineStr">
@@ -10195,7 +10197,7 @@
       <c r="C245" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D245" s="11" t="n">
+      <c r="D245" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E245" s="9" t="inlineStr">
@@ -10309,7 +10311,7 @@
       <c r="C249" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D249" s="11" t="n">
+      <c r="D249" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E249" s="9" t="inlineStr">
@@ -10423,7 +10425,7 @@
       <c r="C253" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D253" s="11" t="n">
+      <c r="D253" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E253" s="9" t="inlineStr">
@@ -10537,7 +10539,7 @@
       <c r="C257" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D257" s="11" t="n">
+      <c r="D257" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E257" s="9" t="inlineStr">
@@ -10651,7 +10653,7 @@
       <c r="C261" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D261" s="11" t="n">
+      <c r="D261" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E261" s="9" t="inlineStr">
@@ -10694,7 +10696,7 @@
       <c r="C262" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D262" s="11" t="n">
+      <c r="D262" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E262" s="9" t="inlineStr">
@@ -10737,7 +10739,7 @@
       <c r="C263" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D263" s="11" t="n">
+      <c r="D263" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E263" s="9" t="inlineStr">
@@ -10780,7 +10782,7 @@
       <c r="C264" s="10" t="n">
         <v>45994</v>
       </c>
-      <c r="D264" s="11" t="n">
+      <c r="D264" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E264" s="9" t="inlineStr">
@@ -10823,7 +10825,7 @@
       <c r="C265" s="10" t="n">
         <v>45995</v>
       </c>
-      <c r="D265" s="11" t="n">
+      <c r="D265" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E265" s="9" t="inlineStr">
@@ -10866,7 +10868,7 @@
       <c r="C266" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D266" s="11" t="n">
+      <c r="D266" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E266" s="9" t="inlineStr">
@@ -10909,7 +10911,7 @@
       <c r="C267" s="10" t="n">
         <v>45997</v>
       </c>
-      <c r="D267" s="11" t="n">
+      <c r="D267" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E267" s="9" t="inlineStr">
@@ -10952,7 +10954,7 @@
       <c r="C268" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D268" s="11" t="n">
+      <c r="D268" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E268" s="9" t="inlineStr">
@@ -10995,7 +10997,7 @@
       <c r="C269" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D269" s="11" t="n">
+      <c r="D269" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E269" s="9" t="inlineStr">
@@ -11038,7 +11040,7 @@
       <c r="C270" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D270" s="11" t="n">
+      <c r="D270" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E270" s="9" t="inlineStr">
@@ -11081,7 +11083,7 @@
       <c r="C271" s="10" t="n">
         <v>46001</v>
       </c>
-      <c r="D271" s="11" t="n">
+      <c r="D271" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E271" s="9" t="inlineStr">
@@ -11124,7 +11126,7 @@
       <c r="C272" s="10" t="n">
         <v>46008</v>
       </c>
-      <c r="D272" s="11" t="n">
+      <c r="D272" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E272" s="9" t="inlineStr">
@@ -11167,7 +11169,7 @@
       <c r="C273" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D273" s="11" t="n">
+      <c r="D273" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E273" s="9" t="inlineStr">
@@ -11210,7 +11212,7 @@
       <c r="C274" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D274" s="11" t="n">
+      <c r="D274" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E274" s="9" t="inlineStr">
@@ -11253,7 +11255,7 @@
       <c r="C275" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D275" s="11" t="n">
+      <c r="D275" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E275" s="9" t="inlineStr">
@@ -11371,7 +11373,7 @@
       <c r="C279" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D279" s="11" t="n">
+      <c r="D279" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E279" s="9" t="inlineStr">
@@ -11414,7 +11416,7 @@
       <c r="C280" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D280" s="11" t="n">
+      <c r="D280" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E280" s="9" t="inlineStr">
@@ -11674,7 +11676,7 @@
       <c r="C290" s="10" t="n">
         <v>45996</v>
       </c>
-      <c r="D290" s="11" t="n">
+      <c r="D290" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E290" s="9" t="inlineStr">
@@ -11717,7 +11719,7 @@
       <c r="C291" s="10" t="n">
         <v>45998</v>
       </c>
-      <c r="D291" s="11" t="n">
+      <c r="D291" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E291" s="9" t="inlineStr">
@@ -11760,7 +11762,7 @@
       <c r="C292" s="10" t="n">
         <v>46000</v>
       </c>
-      <c r="D292" s="11" t="n">
+      <c r="D292" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E292" s="9" t="inlineStr">
@@ -11945,7 +11947,7 @@
       <c r="C299" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D299" s="11" t="n">
+      <c r="D299" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E299" s="9" t="inlineStr">
@@ -11992,7 +11994,7 @@
       <c r="C300" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D300" s="11" t="n">
+      <c r="D300" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E300" s="9" t="inlineStr">
@@ -12039,7 +12041,7 @@
       <c r="C301" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D301" s="11" t="n">
+      <c r="D301" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E301" s="9" t="inlineStr">
@@ -12086,7 +12088,7 @@
       <c r="C302" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D302" s="11" t="n">
+      <c r="D302" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E302" s="9" t="inlineStr">
@@ -12133,7 +12135,7 @@
       <c r="C303" s="10" t="n">
         <v>46020</v>
       </c>
-      <c r="D303" s="11" t="n">
+      <c r="D303" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E303" s="9" t="inlineStr">
@@ -12176,7 +12178,7 @@
       <c r="C304" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D304" s="11" t="n">
+      <c r="D304" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E304" s="9" t="inlineStr">
@@ -12290,7 +12292,7 @@
       <c r="C308" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D308" s="11" t="n">
+      <c r="D308" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E308" s="9" t="inlineStr">
@@ -12479,7 +12481,7 @@
       <c r="C315" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D315" s="11" t="n">
+      <c r="D315" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E315" s="9" t="inlineStr">
@@ -12522,7 +12524,7 @@
       <c r="C316" s="10" t="n">
         <v>46023</v>
       </c>
-      <c r="D316" s="11" t="n">
+      <c r="D316" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E316" s="9" t="inlineStr">
@@ -12782,7 +12784,7 @@
       <c r="C326" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D326" s="11" t="n">
+      <c r="D326" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E326" s="9" t="inlineStr">
@@ -12829,7 +12831,7 @@
       <c r="C327" s="10" t="n">
         <v>46054</v>
       </c>
-      <c r="D327" s="11" t="n">
+      <c r="D327" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E327" s="9" t="inlineStr">
@@ -12947,7 +12949,7 @@
       <c r="C331" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D331" s="11" t="n">
+      <c r="D331" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E331" s="9" t="inlineStr">
@@ -13065,7 +13067,7 @@
       <c r="C335" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D335" s="11" t="n">
+      <c r="D335" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E335" s="9" t="inlineStr">
@@ -13108,7 +13110,7 @@
       <c r="C336" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D336" s="11" t="n">
+      <c r="D336" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E336" s="9" t="inlineStr">
@@ -13222,7 +13224,7 @@
       <c r="C340" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D340" s="11" t="n">
+      <c r="D340" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E340" s="9" t="inlineStr">
@@ -13265,7 +13267,7 @@
       <c r="C341" s="10" t="n">
         <v>46017</v>
       </c>
-      <c r="D341" s="11" t="n">
+      <c r="D341" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E341" s="9" t="inlineStr">
@@ -13379,7 +13381,7 @@
       <c r="C345" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D345" s="11" t="n">
+      <c r="D345" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E345" s="9" t="inlineStr">
@@ -13426,7 +13428,7 @@
       <c r="C346" s="10" t="n">
         <v>46021</v>
       </c>
-      <c r="D346" s="11" t="n">
+      <c r="D346" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E346" s="9" t="inlineStr">
@@ -13544,7 +13546,7 @@
       <c r="C350" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D350" s="11" t="n">
+      <c r="D350" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E350" s="9" t="inlineStr">
@@ -13662,7 +13664,7 @@
       <c r="C354" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D354" s="11" t="n">
+      <c r="D354" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E354" s="9" t="inlineStr">
@@ -13922,7 +13924,7 @@
       <c r="C364" s="10" t="n">
         <v>45991</v>
       </c>
-      <c r="D364" s="11" t="n">
+      <c r="D364" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E364" s="9" t="inlineStr">
@@ -13969,7 +13971,7 @@
       <c r="C365" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D365" s="11" t="n">
+      <c r="D365" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E365" s="9" t="inlineStr">
@@ -14012,7 +14014,7 @@
       <c r="C366" s="10" t="n">
         <v>46009</v>
       </c>
-      <c r="D366" s="11" t="n">
+      <c r="D366" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E366" s="9" t="inlineStr">
@@ -14130,7 +14132,7 @@
       <c r="C370" s="10" t="n">
         <v>46006</v>
       </c>
-      <c r="D370" s="11" t="n">
+      <c r="D370" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E370" s="9" t="inlineStr">
@@ -14244,7 +14246,7 @@
       <c r="C374" s="10" t="n">
         <v>45999</v>
       </c>
-      <c r="D374" s="11" t="n">
+      <c r="D374" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E374" s="9" t="inlineStr">
@@ -14358,7 +14360,7 @@
       <c r="C378" s="10" t="n">
         <v>45993</v>
       </c>
-      <c r="D378" s="11" t="n">
+      <c r="D378" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E378" s="9" t="inlineStr">
@@ -14689,7 +14691,7 @@
       <c r="C391" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D391" s="11" t="n">
+      <c r="D391" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E391" s="9" t="inlineStr">
@@ -14736,7 +14738,7 @@
       <c r="C392" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D392" s="11" t="n">
+      <c r="D392" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E392" s="9" t="inlineStr">
@@ -14783,7 +14785,7 @@
       <c r="C393" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D393" s="11" t="n">
+      <c r="D393" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E393" s="9" t="inlineStr">
@@ -14830,7 +14832,7 @@
       <c r="C394" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D394" s="11" t="n">
+      <c r="D394" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E394" s="9" t="inlineStr">
@@ -14948,7 +14950,7 @@
       <c r="C398" s="10" t="n">
         <v>45992</v>
       </c>
-      <c r="D398" s="11" t="n">
+      <c r="D398" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E398" s="9" t="inlineStr">
@@ -15066,7 +15068,7 @@
       <c r="C402" s="10" t="n">
         <v>46031</v>
       </c>
-      <c r="D402" s="11" t="n">
+      <c r="D402" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E402" s="9" t="inlineStr">
@@ -15184,7 +15186,7 @@
       <c r="C406" s="10" t="n">
         <v>46010</v>
       </c>
-      <c r="D406" s="11" t="n">
+      <c r="D406" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E406" s="9" t="inlineStr">
@@ -15231,7 +15233,7 @@
       <c r="C407" s="10" t="n">
         <v>46022</v>
       </c>
-      <c r="D407" s="11" t="n">
+      <c r="D407" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E407" s="9" t="inlineStr">
@@ -15274,7 +15276,7 @@
       <c r="C408" s="10" t="n">
         <v>46024</v>
       </c>
-      <c r="D408" s="11" t="n">
+      <c r="D408" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E408" s="9" t="inlineStr">
@@ -15534,7 +15536,7 @@
       <c r="C418" s="10" t="n">
         <v>46002</v>
       </c>
-      <c r="D418" s="11" t="n">
+      <c r="D418" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E418" s="9" t="inlineStr">
@@ -15648,7 +15650,7 @@
       <c r="C422" s="10" t="n">
         <v>46013</v>
       </c>
-      <c r="D422" s="11" t="n">
+      <c r="D422" s="67" t="n">
         <v>45992</v>
       </c>
       <c r="E422" s="9" t="inlineStr">
@@ -15753,2472 +15755,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F123"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
-    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
-    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Crystal Lake (sms-crys)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Cash Flow Statement</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Period = Jan 2025-Dec 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Book = Accrual ; Tree = ysi_cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="24" t="n"/>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Period to Date</t>
-        </is>
-      </c>
-      <c r="D5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E5" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Year to Date</t>
-        </is>
-      </c>
-      <c r="F5" s="24" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>4000-0000</t>
-        </is>
-      </c>
-      <c r="B6" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INCOME</t>
-        </is>
-      </c>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="9" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="28" t="n"/>
-      <c r="F7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>4100-0000</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" s="28" t="inlineStr">
-        <is>
-          <t>4500-1001</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Storage Rent</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="n">
-        <v>374474.29</v>
-      </c>
-      <c r="D9" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>374474.29</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>4710-0000</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Less: Concessions</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>-8256.23</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>-8256.23</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="15" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
-        <is>
-          <t>4710-0006</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Bad Debt Write Off</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>-41.03</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>-41.03</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>4710-0007</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Less: Discount - Rent</t>
-        </is>
-      </c>
-      <c r="C12" s="29" t="n">
-        <v>-24</v>
-      </c>
-      <c r="D12" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="29" t="n">
-        <v>-24</v>
-      </c>
-      <c r="F12" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="28" t="inlineStr">
-        <is>
-          <t>4990-0000</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            NET RENT INCOME</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>366153.03</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>366153.03</v>
-      </c>
-      <c r="F13" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="28" t="inlineStr">
-        <is>
-          <t>5000-0001</t>
-        </is>
-      </c>
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise Income</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>739.63</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>739.63</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="28" t="inlineStr">
-        <is>
-          <t>5000-0002</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Merchandise COGS</t>
-        </is>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>-1193.1</v>
-      </c>
-      <c r="D15" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="29" t="n">
-        <v>-1193.1</v>
-      </c>
-      <c r="F15" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="28" t="inlineStr">
-        <is>
-          <t>5000-0003</t>
-        </is>
-      </c>
-      <c r="B16" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Merchandise Sales</t>
-        </is>
-      </c>
-      <c r="C16" s="30" t="n">
-        <v>-453.47</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>-453.47</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="28" t="inlineStr">
-        <is>
-          <t>5000-0010</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>9130.34</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <v>9130.34</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="28" t="inlineStr">
-        <is>
-          <t>5000-0011</t>
-        </is>
-      </c>
-      <c r="B18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Tenant Protection COGS</t>
-        </is>
-      </c>
-      <c r="C18" s="29" t="n">
-        <v>-1705.3</v>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>-1705.3</v>
-      </c>
-      <c r="F18" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="28" t="inlineStr">
-        <is>
-          <t>5000-0012</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            Net Tenant Protection Income</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="n">
-        <v>7425.04</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="30" t="n">
-        <v>7425.04</v>
-      </c>
-      <c r="F19" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="28" t="inlineStr">
-        <is>
-          <t>5000-0013</t>
-        </is>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Phone Convenience Fee</t>
-        </is>
-      </c>
-      <c r="C20" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="D20" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="29" t="n">
-        <v>70</v>
-      </c>
-      <c r="F20" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>5000-1000</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="n">
-        <v>7041.57</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="30" t="n">
-        <v>7041.57</v>
-      </c>
-      <c r="F21" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="28" t="n"/>
-      <c r="E22" s="28" t="n"/>
-      <c r="F22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>5600-0000</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
-        <is>
-          <t>5800-0000</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Late Fee</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>5129</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>5129</v>
-      </c>
-      <c r="F24" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
-        <is>
-          <t>5805-0000</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Administrative Fee</t>
-        </is>
-      </c>
-      <c r="C25" s="29" t="n">
-        <v>1797.86</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>1797.86</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="28" t="inlineStr">
-        <is>
-          <t>5890-0000</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
-        </is>
-      </c>
-      <c r="C26" s="30" t="n">
-        <v>6926.86</v>
-      </c>
-      <c r="D26" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>6926.86</v>
-      </c>
-      <c r="F26" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="32" t="inlineStr">
-        <is>
-          <t>5990-0000</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL INCOME</t>
-        </is>
-      </c>
-      <c r="C28" s="34" t="n">
-        <v>380121.46</v>
-      </c>
-      <c r="D28" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="34" t="n">
-        <v>380121.46</v>
-      </c>
-      <c r="F28" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="28" t="n"/>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="32" t="inlineStr">
-        <is>
-          <t>6000-0000</t>
-        </is>
-      </c>
-      <c r="B30" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> EXPENSES</t>
-        </is>
-      </c>
-      <c r="C30" s="35" t="n"/>
-      <c r="D30" s="35" t="n"/>
-      <c r="E30" s="35" t="n"/>
-      <c r="F30" s="35" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="28" t="n"/>
-      <c r="F31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
-        <is>
-          <t>6050-0000</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
-        <is>
-          <t>6050-0010</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Advertising</t>
-        </is>
-      </c>
-      <c r="C33" s="12" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="12" t="n">
-        <v>38.04</v>
-      </c>
-      <c r="F33" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>6050-0025</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Marketing</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>9572.5</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>9572.5</v>
-      </c>
-      <c r="F34" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
-        <is>
-          <t>6050-0026</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        OnSite Marketing</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>1493.04</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="12" t="n">
-        <v>1493.04</v>
-      </c>
-      <c r="F35" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>6050-0030</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Marketing Other</t>
-        </is>
-      </c>
-      <c r="C36" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="D36" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="29" t="n">
-        <v>32.05</v>
-      </c>
-      <c r="F36" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
-        <is>
-          <t>6050-9999</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
-        </is>
-      </c>
-      <c r="C37" s="30" t="n">
-        <v>11135.63</v>
-      </c>
-      <c r="D37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="30" t="n">
-        <v>11135.63</v>
-      </c>
-      <c r="F37" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="28" t="n"/>
-      <c r="B38" s="9" t="n"/>
-      <c r="C38" s="28" t="n"/>
-      <c r="D38" s="28" t="n"/>
-      <c r="E38" s="28" t="n"/>
-      <c r="F38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="28" t="inlineStr">
-        <is>
-          <t>6100-0000</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="28" t="inlineStr">
-        <is>
-          <t>6110-1050</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Repairs and  Maintenance</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>8208.139999999999</v>
-      </c>
-      <c r="D40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="12" t="n">
-        <v>8208.139999999999</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="28" t="inlineStr">
-        <is>
-          <t>6110-1060</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="n">
-        <v>221.27</v>
-      </c>
-      <c r="D41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="12" t="n">
-        <v>221.27</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="28" t="inlineStr">
-        <is>
-          <t>6110-1175</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Extermination</t>
-        </is>
-      </c>
-      <c r="C42" s="29" t="n">
-        <v>1390</v>
-      </c>
-      <c r="D42" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="29" t="n">
-        <v>1390</v>
-      </c>
-      <c r="F42" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="28" t="inlineStr">
-        <is>
-          <t>6199-9999</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
-        </is>
-      </c>
-      <c r="C43" s="30" t="n">
-        <v>9819.41</v>
-      </c>
-      <c r="D43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="30" t="n">
-        <v>9819.41</v>
-      </c>
-      <c r="F43" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="28" t="n"/>
-      <c r="B44" s="9" t="n"/>
-      <c r="C44" s="28" t="n"/>
-      <c r="D44" s="28" t="n"/>
-      <c r="E44" s="28" t="n"/>
-      <c r="F44" s="28" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="28" t="inlineStr">
-        <is>
-          <t>6200-0000</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    GROUNDS</t>
-        </is>
-      </c>
-      <c r="C45" s="18" t="n"/>
-      <c r="D45" s="18" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="18" t="n"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="28" t="inlineStr">
-        <is>
-          <t>6200-0001</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Trash Disposal</t>
-        </is>
-      </c>
-      <c r="C46" s="29" t="n">
-        <v>4083.9</v>
-      </c>
-      <c r="D46" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="29" t="n">
-        <v>4083.9</v>
-      </c>
-      <c r="F46" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="28" t="inlineStr">
-        <is>
-          <t>6299-9999</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL GROUNDS</t>
-        </is>
-      </c>
-      <c r="C47" s="30" t="n">
-        <v>4083.9</v>
-      </c>
-      <c r="D47" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="30" t="n">
-        <v>4083.9</v>
-      </c>
-      <c r="F47" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="28" t="n"/>
-      <c r="B48" s="9" t="n"/>
-      <c r="C48" s="28" t="n"/>
-      <c r="D48" s="28" t="n"/>
-      <c r="E48" s="28" t="n"/>
-      <c r="F48" s="28" t="n"/>
-    </row>
-    <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="28" t="inlineStr">
-        <is>
-          <t>6400-0000</t>
-        </is>
-      </c>
-      <c r="B49" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    UTILITIES</t>
-        </is>
-      </c>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="28" t="inlineStr">
-        <is>
-          <t>6400-0010</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Electricity</t>
-        </is>
-      </c>
-      <c r="C50" s="12" t="n">
-        <v>3842.72</v>
-      </c>
-      <c r="D50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="12" t="n">
-        <v>3842.72</v>
-      </c>
-      <c r="F50" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="28" t="inlineStr">
-        <is>
-          <t>6400-0046</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Internet Services</t>
-        </is>
-      </c>
-      <c r="C51" s="12" t="n">
-        <v>1739.4</v>
-      </c>
-      <c r="D51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="12" t="n">
-        <v>1739.4</v>
-      </c>
-      <c r="F51" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="28" t="inlineStr">
-        <is>
-          <t>6400-0047</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Telephone Service</t>
-        </is>
-      </c>
-      <c r="C52" s="29" t="n">
-        <v>2503.67</v>
-      </c>
-      <c r="D52" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="29" t="n">
-        <v>2503.67</v>
-      </c>
-      <c r="F52" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1">
-      <c r="A53" s="28" t="inlineStr">
-        <is>
-          <t>6425-0000</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL UTILITIES</t>
-        </is>
-      </c>
-      <c r="C53" s="30" t="n">
-        <v>8085.79</v>
-      </c>
-      <c r="D53" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="30" t="n">
-        <v>8085.79</v>
-      </c>
-      <c r="F53" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1">
-      <c r="A54" s="28" t="inlineStr">
-        <is>
-          <t>6450-0010</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Management Fee</t>
-        </is>
-      </c>
-      <c r="C54" s="29" t="n">
-        <v>18679.74</v>
-      </c>
-      <c r="D54" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="29" t="n">
-        <v>18679.74</v>
-      </c>
-      <c r="F54" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="15" customHeight="1">
-      <c r="A55" s="28" t="inlineStr">
-        <is>
-          <t>6455-0000</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
-        </is>
-      </c>
-      <c r="C55" s="30" t="n">
-        <v>18679.74</v>
-      </c>
-      <c r="D55" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="30" t="n">
-        <v>18679.74</v>
-      </c>
-      <c r="F55" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>6461-0000</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Tax</t>
-        </is>
-      </c>
-      <c r="C56" s="12" t="n">
-        <v>60298.44</v>
-      </c>
-      <c r="D56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="12" t="n">
-        <v>60298.44</v>
-      </c>
-      <c r="F56" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="28" t="inlineStr">
-        <is>
-          <t>6461-1000</t>
-        </is>
-      </c>
-      <c r="B57" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Property Insurance</t>
-        </is>
-      </c>
-      <c r="C57" s="29" t="n">
-        <v>8892.959999999999</v>
-      </c>
-      <c r="D57" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="29" t="n">
-        <v>8892.959999999999</v>
-      </c>
-      <c r="F57" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="28" t="inlineStr">
-        <is>
-          <t>6470-0000</t>
-        </is>
-      </c>
-      <c r="B58" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
-        </is>
-      </c>
-      <c r="C58" s="30" t="n">
-        <v>69191.39999999999</v>
-      </c>
-      <c r="D58" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="30" t="n">
-        <v>69191.39999999999</v>
-      </c>
-      <c r="F58" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="28" t="inlineStr">
-        <is>
-          <t>7000-0009</t>
-        </is>
-      </c>
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Meals &amp; Entertainment</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="D59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="12" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="F59" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="28" t="inlineStr">
-        <is>
-          <t>7000-0013</t>
-        </is>
-      </c>
-      <c r="B60" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Vehicle Expense</t>
-        </is>
-      </c>
-      <c r="C60" s="12" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="D60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="12" t="n">
-        <v>66.15000000000001</v>
-      </c>
-      <c r="F60" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" ht="15" customHeight="1">
-      <c r="A61" s="28" t="inlineStr">
-        <is>
-          <t>7000-0026</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Software</t>
-        </is>
-      </c>
-      <c r="C61" s="12" t="n">
-        <v>4742.19</v>
-      </c>
-      <c r="D61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="12" t="n">
-        <v>4742.19</v>
-      </c>
-      <c r="F61" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="28" t="inlineStr">
-        <is>
-          <t>7000-0045</t>
-        </is>
-      </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Bank Charges Expense</t>
-        </is>
-      </c>
-      <c r="C62" s="12" t="n">
-        <v>2477.67</v>
-      </c>
-      <c r="D62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="12" t="n">
-        <v>2477.67</v>
-      </c>
-      <c r="F62" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" ht="15" customHeight="1">
-      <c r="A63" s="28" t="inlineStr">
-        <is>
-          <t>7000-0047</t>
-        </is>
-      </c>
-      <c r="B63" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Credit Card Processing Fees</t>
-        </is>
-      </c>
-      <c r="C63" s="12" t="n">
-        <v>7914.5</v>
-      </c>
-      <c r="D63" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="12" t="n">
-        <v>7914.5</v>
-      </c>
-      <c r="F63" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1">
-      <c r="A64" s="28" t="inlineStr">
-        <is>
-          <t>7000-0050</t>
-        </is>
-      </c>
-      <c r="B64" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Postage and Shipping Fees</t>
-        </is>
-      </c>
-      <c r="C64" s="12" t="n">
-        <v>203.66</v>
-      </c>
-      <c r="D64" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="12" t="n">
-        <v>203.66</v>
-      </c>
-      <c r="F64" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="28" t="inlineStr">
-        <is>
-          <t>7000-0054</t>
-        </is>
-      </c>
-      <c r="B65" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Travel Expenses</t>
-        </is>
-      </c>
-      <c r="C65" s="12" t="n">
-        <v>73.83</v>
-      </c>
-      <c r="D65" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="12" t="n">
-        <v>73.83</v>
-      </c>
-      <c r="F65" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" ht="15" customHeight="1">
-      <c r="A66" s="28" t="inlineStr">
-        <is>
-          <t>7000-0060</t>
-        </is>
-      </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Office Supplies</t>
-        </is>
-      </c>
-      <c r="C66" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="D66" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="29" t="n">
-        <v>48</v>
-      </c>
-      <c r="F66" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>7000-1000</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
-        </is>
-      </c>
-      <c r="C67" s="30" t="n">
-        <v>15540.01</v>
-      </c>
-      <c r="D67" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" s="30" t="n">
-        <v>15540.01</v>
-      </c>
-      <c r="F67" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="28" t="n"/>
-      <c r="B68" s="9" t="n"/>
-      <c r="C68" s="28" t="n"/>
-      <c r="D68" s="28" t="n"/>
-      <c r="E68" s="28" t="n"/>
-      <c r="F68" s="28" t="n"/>
-    </row>
-    <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="28" t="inlineStr">
-        <is>
-          <t>7200-0000</t>
-        </is>
-      </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-    </row>
-    <row r="70" ht="15" customHeight="1">
-      <c r="A70" s="28" t="inlineStr">
-        <is>
-          <t>7200-0001</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Answering Service</t>
-        </is>
-      </c>
-      <c r="C70" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="D70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="12" t="n">
-        <v>-117.06</v>
-      </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1">
-      <c r="A71" s="28" t="inlineStr">
-        <is>
-          <t>7200-0002</t>
-        </is>
-      </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Communication Center</t>
-        </is>
-      </c>
-      <c r="C71" s="12" t="n">
-        <v>7954.49</v>
-      </c>
-      <c r="D71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="12" t="n">
-        <v>7954.49</v>
-      </c>
-      <c r="F71" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" ht="15" customHeight="1">
-      <c r="A72" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C72" s="12" t="n">
-        <v>1614.25</v>
-      </c>
-      <c r="D72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="12" t="n">
-        <v>1614.25</v>
-      </c>
-      <c r="F72" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="28" t="inlineStr">
-        <is>
-          <t>7200-0020</t>
-        </is>
-      </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Professional Fees</t>
-        </is>
-      </c>
-      <c r="C73" s="29" t="n">
-        <v>138</v>
-      </c>
-      <c r="D73" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" s="29" t="n">
-        <v>138</v>
-      </c>
-      <c r="F73" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="28" t="inlineStr">
-        <is>
-          <t>7200-0100</t>
-        </is>
-      </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
-        </is>
-      </c>
-      <c r="C74" s="30" t="n">
-        <v>9589.68</v>
-      </c>
-      <c r="D74" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="30" t="n">
-        <v>9589.68</v>
-      </c>
-      <c r="F74" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="28" t="n"/>
-      <c r="B75" s="9" t="n"/>
-      <c r="C75" s="28" t="n"/>
-      <c r="D75" s="28" t="n"/>
-      <c r="E75" s="28" t="n"/>
-      <c r="F75" s="28" t="n"/>
-    </row>
-    <row r="76" ht="15" customHeight="1">
-      <c r="A76" s="28" t="inlineStr">
-        <is>
-          <t>7310-0000</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="28" t="inlineStr">
-        <is>
-          <t>7310-0005</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          Supervisory Payroll Expense</t>
-        </is>
-      </c>
-      <c r="C77" s="29" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D77" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="29" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F77" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="28" t="inlineStr">
-        <is>
-          <t>7310-0100</t>
-        </is>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
-        </is>
-      </c>
-      <c r="C78" s="36" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D78" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="36" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F78" s="36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" ht="15" customHeight="1">
-      <c r="A79" s="28" t="inlineStr">
-        <is>
-          <t>7500-0000</t>
-        </is>
-      </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL PAYROLL</t>
-        </is>
-      </c>
-      <c r="C79" s="30" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="D79" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" s="30" t="n">
-        <v>5027.54</v>
-      </c>
-      <c r="F79" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" ht="15" customHeight="1">
-      <c r="A80" s="28" t="n"/>
-      <c r="B80" s="9" t="n"/>
-      <c r="C80" s="31" t="n"/>
-      <c r="D80" s="31" t="n"/>
-      <c r="E80" s="31" t="n"/>
-      <c r="F80" s="31" t="n"/>
-    </row>
-    <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
-        <is>
-          <t>7999-9000</t>
-        </is>
-      </c>
-      <c r="B81" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
-        </is>
-      </c>
-      <c r="C81" s="34" t="n">
-        <v>151153.1</v>
-      </c>
-      <c r="D81" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="34" t="n">
-        <v>151153.1</v>
-      </c>
-      <c r="F81" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="28" t="n"/>
-      <c r="B82" s="9" t="n"/>
-      <c r="C82" s="37" t="n"/>
-      <c r="D82" s="37" t="n"/>
-      <c r="E82" s="37" t="n"/>
-      <c r="F82" s="37" t="n"/>
-    </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="38" t="inlineStr">
-        <is>
-          <t>7999-9999</t>
-        </is>
-      </c>
-      <c r="B83" s="39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET OPERATING INCOME</t>
-        </is>
-      </c>
-      <c r="C83" s="40" t="n">
-        <v>228968.36</v>
-      </c>
-      <c r="D83" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="40" t="n">
-        <v>228968.36</v>
-      </c>
-      <c r="F83" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1">
-      <c r="A84" s="28" t="inlineStr">
-        <is>
-          <t>8170-0000</t>
-        </is>
-      </c>
-      <c r="B84" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Signage and Awnings</t>
-        </is>
-      </c>
-      <c r="C84" s="41" t="n">
-        <v>841.5700000000001</v>
-      </c>
-      <c r="D84" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="41" t="n">
-        <v>841.5700000000001</v>
-      </c>
-      <c r="F84" s="41" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1">
-      <c r="A85" s="28" t="inlineStr">
-        <is>
-          <t>8179-9999</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Repairs Major</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="n">
-        <v>5385</v>
-      </c>
-      <c r="D85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="12" t="n">
-        <v>5385</v>
-      </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1">
-      <c r="A86" s="28" t="inlineStr">
-        <is>
-          <t>8389-9999</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Miscelleneous Non-Operating Expense</t>
-        </is>
-      </c>
-      <c r="C86" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="D86" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="29" t="n">
-        <v>15</v>
-      </c>
-      <c r="F86" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1">
-      <c r="A87" s="28" t="inlineStr">
-        <is>
-          <t>8390-0000</t>
-        </is>
-      </c>
-      <c r="B87" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL NON-RECURRING EXPENSES</t>
-        </is>
-      </c>
-      <c r="C87" s="30" t="n">
-        <v>6241.57</v>
-      </c>
-      <c r="D87" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="30" t="n">
-        <v>6241.57</v>
-      </c>
-      <c r="F87" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1">
-      <c r="A88" s="28" t="inlineStr">
-        <is>
-          <t>8540-0000</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Loan Interest</t>
-        </is>
-      </c>
-      <c r="C88" s="29" t="n">
-        <v>83770.84</v>
-      </c>
-      <c r="D88" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="29" t="n">
-        <v>83770.84</v>
-      </c>
-      <c r="F88" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1">
-      <c r="A89" s="28" t="inlineStr">
-        <is>
-          <t>8590-0000</t>
-        </is>
-      </c>
-      <c r="B89" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
-        </is>
-      </c>
-      <c r="C89" s="30" t="n">
-        <v>83770.84</v>
-      </c>
-      <c r="D89" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="30" t="n">
-        <v>83770.84</v>
-      </c>
-      <c r="F89" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="28" t="n"/>
-      <c r="B90" s="9" t="n"/>
-      <c r="C90" s="31" t="n"/>
-      <c r="D90" s="31" t="n"/>
-      <c r="E90" s="31" t="n"/>
-      <c r="F90" s="31" t="n"/>
-    </row>
-    <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="32" t="inlineStr">
-        <is>
-          <t>8990-0000</t>
-        </is>
-      </c>
-      <c r="B91" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                TOTAL EXPENSES</t>
-        </is>
-      </c>
-      <c r="C91" s="34" t="n">
-        <v>90012.41</v>
-      </c>
-      <c r="D91" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="34" t="n">
-        <v>90012.41</v>
-      </c>
-      <c r="F91" s="34" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="28" t="n"/>
-      <c r="B92" s="9" t="n"/>
-      <c r="C92" s="37" t="n"/>
-      <c r="D92" s="37" t="n"/>
-      <c r="E92" s="37" t="n"/>
-      <c r="F92" s="37" t="n"/>
-    </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="32" t="inlineStr">
-        <is>
-          <t>9090-0000</t>
-        </is>
-      </c>
-      <c r="B93" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    NET INCOME</t>
-        </is>
-      </c>
-      <c r="C93" s="42" t="n">
-        <v>138955.95</v>
-      </c>
-      <c r="D93" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="42" t="n">
-        <v>138955.95</v>
-      </c>
-      <c r="F93" s="42" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="28" t="n"/>
-      <c r="B94" s="9" t="n"/>
-      <c r="C94" s="43" t="n"/>
-      <c r="D94" s="43" t="n"/>
-      <c r="E94" s="43" t="n"/>
-      <c r="F94" s="43" t="n"/>
-    </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="28" t="n"/>
-      <c r="B95" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C95" s="18" t="n"/>
-      <c r="D95" s="18" t="n"/>
-      <c r="E95" s="18" t="n"/>
-      <c r="F95" s="18" t="n"/>
-    </row>
-    <row r="96" ht="15" customHeight="1">
-      <c r="A96" s="28" t="n"/>
-      <c r="B96" s="9" t="n"/>
-      <c r="C96" s="28" t="n"/>
-      <c r="D96" s="28" t="n"/>
-      <c r="E96" s="28" t="n"/>
-      <c r="F96" s="28" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1">
-      <c r="A97" s="28" t="inlineStr">
-        <is>
-          <t>1300-0000</t>
-        </is>
-      </c>
-      <c r="B97" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Receivable</t>
-        </is>
-      </c>
-      <c r="C97" s="12" t="n">
-        <v>-10322.33</v>
-      </c>
-      <c r="D97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>-10322.33</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="28" t="inlineStr">
-        <is>
-          <t>1350-0001</t>
-        </is>
-      </c>
-      <c r="B98" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Pre-Paid Insurance</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="n">
-        <v>-35.04</v>
-      </c>
-      <c r="D98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>-35.04</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1">
-      <c r="A99" s="28" t="inlineStr">
-        <is>
-          <t>1910-0001</t>
-        </is>
-      </c>
-      <c r="B99" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Disputed Bank Transaction</t>
-        </is>
-      </c>
-      <c r="C99" s="12" t="n">
-        <v>-1516</v>
-      </c>
-      <c r="D99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>-1516</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1">
-      <c r="A100" s="28" t="inlineStr">
-        <is>
-          <t>2110-0000</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Note 1 Principal</t>
-        </is>
-      </c>
-      <c r="C100" s="12" t="n">
-        <v>-27213.04</v>
-      </c>
-      <c r="D100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>-27213.04</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" ht="15" customHeight="1">
-      <c r="A101" s="28" t="inlineStr">
-        <is>
-          <t>2150-0020</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Due To/(From) Other Property</t>
-        </is>
-      </c>
-      <c r="C101" s="12" t="n">
-        <v>3079.52</v>
-      </c>
-      <c r="D101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>3079.52</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>2200-0000</t>
-        </is>
-      </c>
-      <c r="B102" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Accounts Payable</t>
-        </is>
-      </c>
-      <c r="C102" s="12" t="n">
-        <v>3331.87</v>
-      </c>
-      <c r="D102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>3331.87</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1">
-      <c r="A103" s="28" t="inlineStr">
-        <is>
-          <t>2210-0000</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Prepaid Rent</t>
-        </is>
-      </c>
-      <c r="C103" s="29" t="n">
-        <v>-509.92</v>
-      </c>
-      <c r="D103" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="29" t="n">
-        <v>-509.92</v>
-      </c>
-      <c r="F103" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1">
-      <c r="A104" s="28" t="inlineStr">
-        <is>
-          <t>2250-0000</t>
-        </is>
-      </c>
-      <c r="B104" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Tenant Deposits</t>
-        </is>
-      </c>
-      <c r="C104" s="30" t="n">
-        <v>-940</v>
-      </c>
-      <c r="D104" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" s="30" t="n">
-        <v>-940</v>
-      </c>
-      <c r="F104" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="28" t="inlineStr">
-        <is>
-          <t>2270-0010</t>
-        </is>
-      </c>
-      <c r="B105" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Tenant Protection Net Payable</t>
-        </is>
-      </c>
-      <c r="C105" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="D105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="28" t="inlineStr">
-        <is>
-          <t>2305-0000</t>
-        </is>
-      </c>
-      <c r="B106" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Real Estate Tax Accrual</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>2206.68</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>2206.68</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="28" t="inlineStr">
-        <is>
-          <t>2310-0000</t>
-        </is>
-      </c>
-      <c r="B107" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Sales Tax Collected</t>
-        </is>
-      </c>
-      <c r="C107" s="12" t="n">
-        <v>1411.57</v>
-      </c>
-      <c r="D107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>1411.57</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" s="28" t="inlineStr">
-        <is>
-          <t>2640-0998</t>
-        </is>
-      </c>
-      <c r="B108" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Expense Accrual</t>
-        </is>
-      </c>
-      <c r="C108" s="12" t="n">
-        <v>2340.91</v>
-      </c>
-      <c r="D108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>2340.91</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" s="28" t="inlineStr">
-        <is>
-          <t>2640-0999</t>
-        </is>
-      </c>
-      <c r="B109" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Payroll Accrual</t>
-        </is>
-      </c>
-      <c r="C109" s="12" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="D109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>27.48</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1">
-      <c r="A110" s="28" t="inlineStr">
-        <is>
-          <t>3300-0000</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Owner Distributions</t>
-        </is>
-      </c>
-      <c r="C110" s="12" t="n">
-        <v>-104335.19</v>
-      </c>
-      <c r="D110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>-104335.19</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1">
-      <c r="A111" s="28" t="inlineStr">
-        <is>
-          <t>7200-0003</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        Auction Costs</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="n">
-        <v>-1614.25</v>
-      </c>
-      <c r="D111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v>-1614.25</v>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1">
-      <c r="A112" s="28" t="n"/>
-      <c r="B112" s="9" t="n"/>
-      <c r="C112" s="31" t="n"/>
-      <c r="D112" s="31" t="n"/>
-      <c r="E112" s="31" t="n"/>
-      <c r="F112" s="31" t="n"/>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="28" t="n"/>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
-        </is>
-      </c>
-      <c r="C113" s="30" t="n">
-        <v>-134075.74</v>
-      </c>
-      <c r="D113" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="30" t="n">
-        <v>-134075.74</v>
-      </c>
-      <c r="F113" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1">
-      <c r="A114" s="28" t="n"/>
-      <c r="B114" s="9" t="n"/>
-      <c r="C114" s="31" t="n"/>
-      <c r="D114" s="31" t="n"/>
-      <c r="E114" s="31" t="n"/>
-      <c r="F114" s="31" t="n"/>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="28" t="n"/>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    CASH FLOW</t>
-        </is>
-      </c>
-      <c r="C115" s="30" t="n">
-        <v>4880.21</v>
-      </c>
-      <c r="D115" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="30" t="n">
-        <v>4880.21</v>
-      </c>
-      <c r="F115" s="30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="28" t="n"/>
-    </row>
-    <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="28" t="n"/>
-      <c r="B117" s="33" t="inlineStr">
-        <is>
-          <t>Period to Date</t>
-        </is>
-      </c>
-      <c r="C117" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D117" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E117" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F117" s="28" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="28" t="inlineStr">
-        <is>
-          <t>1110-4974</t>
-        </is>
-      </c>
-      <c r="B118" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Crystal Lake</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="n">
-        <v>21679.59</v>
-      </c>
-      <c r="D118" s="12" t="n">
-        <v>28174.05</v>
-      </c>
-      <c r="E118" s="12" t="n">
-        <v>6494.46</v>
-      </c>
-      <c r="F118" s="28" t="n"/>
-    </row>
-    <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="28" t="n"/>
-      <c r="B119" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C119" s="44" t="n">
-        <v>21679.59</v>
-      </c>
-      <c r="D119" s="44" t="n">
-        <v>28174.05</v>
-      </c>
-      <c r="E119" s="44" t="n">
-        <v>6494.46</v>
-      </c>
-      <c r="F119" s="28" t="n"/>
-    </row>
-    <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="28" t="n"/>
-    </row>
-    <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="28" t="n"/>
-      <c r="B121" s="33" t="inlineStr">
-        <is>
-          <t>Year to Date</t>
-        </is>
-      </c>
-      <c r="C121" s="32" t="inlineStr">
-        <is>
-          <t>Beginning Balance</t>
-        </is>
-      </c>
-      <c r="D121" s="32" t="inlineStr">
-        <is>
-          <t>Ending Balance</t>
-        </is>
-      </c>
-      <c r="E121" s="32" t="inlineStr">
-        <is>
-          <t>Difference</t>
-        </is>
-      </c>
-      <c r="F121" s="28" t="n"/>
-    </row>
-    <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="28" t="inlineStr">
-        <is>
-          <t>1110-4974</t>
-        </is>
-      </c>
-      <c r="B122" s="9" t="inlineStr">
-        <is>
-          <t>Storsafe Management Solutions - Crystal Lake</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="n">
-        <v>21679.59</v>
-      </c>
-      <c r="D122" s="12" t="n">
-        <v>28174.05</v>
-      </c>
-      <c r="E122" s="12" t="n">
-        <v>6494.46</v>
-      </c>
-      <c r="F122" s="28" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="28" t="n"/>
-      <c r="B123" s="33" t="inlineStr">
-        <is>
-          <t>Total Cash</t>
-        </is>
-      </c>
-      <c r="C123" s="44" t="n">
-        <v>21679.59</v>
-      </c>
-      <c r="D123" s="44" t="n">
-        <v>28174.05</v>
-      </c>
-      <c r="E123" s="44" t="n">
-        <v>6494.46</v>
-      </c>
-      <c r="F123" s="28" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -22182,4 +19718,2437 @@
   <pageMargins left="0.7" right="0.7" top="0.7" bottom="0.7" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="5" fitToHeight="990" firstPageNumber="1" useFirstPageNumber="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F122"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.142857142857141" defaultRowHeight="12.75"/>
+  <cols>
+    <col width="11.4285714285714" customWidth="1" min="1" max="1"/>
+    <col width="37.1428571428571" customWidth="1" min="2" max="2"/>
+    <col width="17.1428571428571" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Crystal Lake (sms-crys)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Cash Flow Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Period = Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Book = Accrual ; Tree = ysi_cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="24" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Period to Date</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Year to Date</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>4000-0000</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> INCOME</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="27" t="n"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" s="28" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="28" t="n"/>
+      <c r="D7" s="28" t="n"/>
+      <c r="E7" s="28" t="n"/>
+      <c r="F7" s="28" t="n"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>4100-0000</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>4500-1001</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Storage Rent</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="n">
+        <v>33178.25</v>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>374474.29</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>4710-0000</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Less: Concessions</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>-892.41</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>-8256.23</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
+        <is>
+          <t>4710-0006</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Bad Debt Write Off</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>-41.03</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>-41.03</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>4710-0007</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Less: Discount - Rent</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>-24</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>-24</v>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="28" t="inlineStr">
+        <is>
+          <t>4990-0000</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            NET RENT INCOME</t>
+        </is>
+      </c>
+      <c r="C13" s="30" t="n">
+        <v>32220.81</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>366153.03</v>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1">
+      <c r="A14" s="28" t="inlineStr">
+        <is>
+          <t>5000-0001</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise Income</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>739.63</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>5000-0002</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Merchandise COGS</t>
+        </is>
+      </c>
+      <c r="C15" s="29" t="n">
+        <v>-100</v>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>-1193.1</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>5000-0003</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Merchandise Sales</t>
+        </is>
+      </c>
+      <c r="C16" s="30" t="n">
+        <v>-80.01000000000001</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>-453.47</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="A17" s="28" t="inlineStr">
+        <is>
+          <t>5000-0010</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>697.51</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>9130.34</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>5000-0011</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Tenant Protection COGS</t>
+        </is>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>-112.93</v>
+      </c>
+      <c r="D18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="29" t="n">
+        <v>-1705.3</v>
+      </c>
+      <c r="F18" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>5000-0012</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            Net Tenant Protection Income</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="n">
+        <v>584.58</v>
+      </c>
+      <c r="D19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="30" t="n">
+        <v>7425.04</v>
+      </c>
+      <c r="F19" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>5000-0013</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Phone Convenience Fee</t>
+        </is>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="29" t="n">
+        <v>70</v>
+      </c>
+      <c r="F20" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
+          <t>5000-1000</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ANCILLARY INCOME</t>
+        </is>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>504.57</v>
+      </c>
+      <c r="D21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="30" t="n">
+        <v>7041.57</v>
+      </c>
+      <c r="F21" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="28" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>5600-0000</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
+          <t>5800-0000</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Late Fee</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>5129</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
+          <t>5805-0000</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Administrative Fee</t>
+        </is>
+      </c>
+      <c r="C25" s="29" t="n">
+        <v>87</v>
+      </c>
+      <c r="D25" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="29" t="n">
+        <v>1797.86</v>
+      </c>
+      <c r="F25" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
+        <is>
+          <t>5890-0000</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL OTHER INCOME</t>
+        </is>
+      </c>
+      <c r="C26" s="30" t="n">
+        <v>87</v>
+      </c>
+      <c r="D26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="30" t="n">
+        <v>6926.86</v>
+      </c>
+      <c r="F26" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" s="28" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>5990-0000</t>
+        </is>
+      </c>
+      <c r="B28" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL INCOME</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="n">
+        <v>32812.38</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="34" t="n">
+        <v>380121.46</v>
+      </c>
+      <c r="F28" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" s="28" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>6000-0000</t>
+        </is>
+      </c>
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> EXPENSES</t>
+        </is>
+      </c>
+      <c r="C30" s="35" t="n"/>
+      <c r="D30" s="35" t="n"/>
+      <c r="E30" s="35" t="n"/>
+      <c r="F30" s="35" t="n"/>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="28" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="28" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>6050-0000</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADVERTISING and MARKETING</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>6050-0010</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Advertising</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>6050-0025</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Marketing</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>855.35</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>9572.5</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="28" t="inlineStr">
+        <is>
+          <t>6050-0026</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        OnSite Marketing</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>124.78</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>1493.04</v>
+      </c>
+      <c r="F35" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>6050-0030</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Marketing Other</t>
+        </is>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="29" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="F36" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="28" t="inlineStr">
+        <is>
+          <t>6050-9999</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            ADVERTISING and MARKETING TOTAL</t>
+        </is>
+      </c>
+      <c r="C37" s="30" t="n">
+        <v>980.13</v>
+      </c>
+      <c r="D37" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="30" t="n">
+        <v>11135.63</v>
+      </c>
+      <c r="F37" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1">
+      <c r="A38" s="28" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="28" t="n"/>
+      <c r="D38" s="28" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="28" t="n"/>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="A39" s="28" t="inlineStr">
+        <is>
+          <t>6100-0000</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>6110-1050</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Repairs and  Maintenance</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>444.19</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>8208.139999999999</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>6110-1060</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Maintenance Tools and Supplies</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>221.27</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>6110-1175</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Extermination</t>
+        </is>
+      </c>
+      <c r="C42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>1390</v>
+      </c>
+      <c r="F42" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>6199-9999</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL REPAIRS AND MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="C43" s="30" t="n">
+        <v>444.19</v>
+      </c>
+      <c r="D43" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="30" t="n">
+        <v>9819.41</v>
+      </c>
+      <c r="F43" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="28" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="28" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="28" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="28" t="inlineStr">
+        <is>
+          <t>6200-0000</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    GROUNDS</t>
+        </is>
+      </c>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>6200-0001</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Trash Disposal</t>
+        </is>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>559.3</v>
+      </c>
+      <c r="D46" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>4083.9</v>
+      </c>
+      <c r="F46" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1">
+      <c r="A47" s="28" t="inlineStr">
+        <is>
+          <t>6299-9999</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL GROUNDS</t>
+        </is>
+      </c>
+      <c r="C47" s="30" t="n">
+        <v>559.3</v>
+      </c>
+      <c r="D47" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="30" t="n">
+        <v>4083.9</v>
+      </c>
+      <c r="F47" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="28" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="28" t="n"/>
+      <c r="D48" s="28" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="28" t="n"/>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="28" t="inlineStr">
+        <is>
+          <t>6400-0000</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    UTILITIES</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>6400-0010</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Electricity</t>
+        </is>
+      </c>
+      <c r="C50" s="12" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="D50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="12" t="n">
+        <v>3842.72</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1">
+      <c r="A51" s="28" t="inlineStr">
+        <is>
+          <t>6400-0046</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Internet Services</t>
+        </is>
+      </c>
+      <c r="C51" s="12" t="n">
+        <v>148.95</v>
+      </c>
+      <c r="D51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="12" t="n">
+        <v>1739.4</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1">
+      <c r="A52" s="28" t="inlineStr">
+        <is>
+          <t>6400-0047</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Telephone Service</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="n">
+        <v>241.46</v>
+      </c>
+      <c r="D52" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="29" t="n">
+        <v>2503.67</v>
+      </c>
+      <c r="F52" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1">
+      <c r="A53" s="28" t="inlineStr">
+        <is>
+          <t>6425-0000</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL UTILITIES</t>
+        </is>
+      </c>
+      <c r="C53" s="30" t="n">
+        <v>392.38</v>
+      </c>
+      <c r="D53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="30" t="n">
+        <v>8085.79</v>
+      </c>
+      <c r="F53" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1">
+      <c r="A54" s="28" t="inlineStr">
+        <is>
+          <t>6450-0010</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Management Fee</t>
+        </is>
+      </c>
+      <c r="C54" s="29" t="n">
+        <v>1531.41</v>
+      </c>
+      <c r="D54" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="29" t="n">
+        <v>18679.74</v>
+      </c>
+      <c r="F54" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="28" t="inlineStr">
+        <is>
+          <t>6455-0000</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL ADMINISTRATIVE &amp; MANAGEMENT EXPENSES</t>
+        </is>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>1531.41</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="30" t="n">
+        <v>18679.74</v>
+      </c>
+      <c r="F55" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>6461-0000</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Tax</t>
+        </is>
+      </c>
+      <c r="C56" s="12" t="n">
+        <v>5024.87</v>
+      </c>
+      <c r="D56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="12" t="n">
+        <v>60298.44</v>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>6461-1000</t>
+        </is>
+      </c>
+      <c r="B57" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Property Insurance</t>
+        </is>
+      </c>
+      <c r="C57" s="29" t="n">
+        <v>741.08</v>
+      </c>
+      <c r="D57" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="29" t="n">
+        <v>8892.959999999999</v>
+      </c>
+      <c r="F57" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>6470-0000</t>
+        </is>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROPERTY TAXES &amp; INSURANCE</t>
+        </is>
+      </c>
+      <c r="C58" s="30" t="n">
+        <v>5765.95</v>
+      </c>
+      <c r="D58" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="30" t="n">
+        <v>69191.39999999999</v>
+      </c>
+      <c r="F58" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1">
+      <c r="A59" s="28" t="inlineStr">
+        <is>
+          <t>7000-0009</t>
+        </is>
+      </c>
+      <c r="B59" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Meals &amp; Entertainment</t>
+        </is>
+      </c>
+      <c r="C59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="12" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1">
+      <c r="A60" s="28" t="inlineStr">
+        <is>
+          <t>7000-0013</t>
+        </is>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Vehicle Expense</t>
+        </is>
+      </c>
+      <c r="C60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="12" t="n">
+        <v>66.15000000000001</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>7000-0026</t>
+        </is>
+      </c>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Software</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="n">
+        <v>315.04</v>
+      </c>
+      <c r="D61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>4742.19</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1">
+      <c r="A62" s="28" t="inlineStr">
+        <is>
+          <t>7000-0045</t>
+        </is>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Bank Charges Expense</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="n">
+        <v>307.21</v>
+      </c>
+      <c r="D62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>2477.67</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="28" t="inlineStr">
+        <is>
+          <t>7000-0047</t>
+        </is>
+      </c>
+      <c r="B63" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Credit Card Processing Fees</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="n">
+        <v>735.2</v>
+      </c>
+      <c r="D63" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>7914.5</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="28" t="inlineStr">
+        <is>
+          <t>7000-0050</t>
+        </is>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Postage and Shipping Fees</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="D64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>203.66</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1">
+      <c r="A65" s="28" t="inlineStr">
+        <is>
+          <t>7000-0054</t>
+        </is>
+      </c>
+      <c r="B65" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Travel Expenses</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>73.83</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1">
+      <c r="A66" s="28" t="inlineStr">
+        <is>
+          <t>7000-0060</t>
+        </is>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Office Supplies</t>
+        </is>
+      </c>
+      <c r="C66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="29" t="n">
+        <v>48</v>
+      </c>
+      <c r="F66" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="28" t="inlineStr">
+        <is>
+          <t>7000-1000</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL G and A EXPENSE</t>
+        </is>
+      </c>
+      <c r="C67" s="30" t="n">
+        <v>1402.45</v>
+      </c>
+      <c r="D67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="30" t="n">
+        <v>15540.01</v>
+      </c>
+      <c r="F67" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1">
+      <c r="A68" s="28" t="n"/>
+      <c r="B68" s="9" t="n"/>
+      <c r="C68" s="28" t="n"/>
+      <c r="D68" s="28" t="n"/>
+      <c r="E68" s="28" t="n"/>
+      <c r="F68" s="28" t="n"/>
+    </row>
+    <row r="69" ht="15" customHeight="1">
+      <c r="A69" s="28" t="inlineStr">
+        <is>
+          <t>7200-0000</t>
+        </is>
+      </c>
+      <c r="B69" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+    </row>
+    <row r="70" ht="15" customHeight="1">
+      <c r="A70" s="28" t="inlineStr">
+        <is>
+          <t>7200-0001</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Answering Service</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>-117.06</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1">
+      <c r="A71" s="28" t="inlineStr">
+        <is>
+          <t>7200-0002</t>
+        </is>
+      </c>
+      <c r="B71" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Communication Center</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="n">
+        <v>626.95</v>
+      </c>
+      <c r="D71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>7954.49</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1">
+      <c r="A72" s="28" t="inlineStr">
+        <is>
+          <t>7200-0003</t>
+        </is>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Auction Costs</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>1614.25</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="28" t="inlineStr">
+        <is>
+          <t>7200-0020</t>
+        </is>
+      </c>
+      <c r="B73" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Professional Fees</t>
+        </is>
+      </c>
+      <c r="C73" s="29" t="n">
+        <v>17</v>
+      </c>
+      <c r="D73" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="29" t="n">
+        <v>138</v>
+      </c>
+      <c r="F73" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1">
+      <c r="A74" s="28" t="inlineStr">
+        <is>
+          <t>7200-0100</t>
+        </is>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PROFESSIONAL FEES</t>
+        </is>
+      </c>
+      <c r="C74" s="30" t="n">
+        <v>653.95</v>
+      </c>
+      <c r="D74" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="30" t="n">
+        <v>9589.68</v>
+      </c>
+      <c r="F74" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1">
+      <c r="A75" s="28" t="n"/>
+      <c r="B75" s="9" t="n"/>
+      <c r="C75" s="28" t="n"/>
+      <c r="D75" s="28" t="n"/>
+      <c r="E75" s="28" t="n"/>
+      <c r="F75" s="28" t="n"/>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="28" t="inlineStr">
+        <is>
+          <t>7310-0000</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1">
+      <c r="A77" s="28" t="inlineStr">
+        <is>
+          <t>7310-0005</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Supervisory Payroll Expense</t>
+        </is>
+      </c>
+      <c r="C77" s="29" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D77" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="29" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F77" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1">
+      <c r="A78" s="28" t="inlineStr">
+        <is>
+          <t>7310-0100</t>
+        </is>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL SUPERVISORY PAYROLL</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D78" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="36" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F78" s="36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1">
+      <c r="A79" s="28" t="inlineStr">
+        <is>
+          <t>7500-0000</t>
+        </is>
+      </c>
+      <c r="B79" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL PAYROLL</t>
+        </is>
+      </c>
+      <c r="C79" s="30" t="n">
+        <v>439.57</v>
+      </c>
+      <c r="D79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="30" t="n">
+        <v>5027.54</v>
+      </c>
+      <c r="F79" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="28" t="n"/>
+      <c r="B80" s="9" t="n"/>
+      <c r="C80" s="31" t="n"/>
+      <c r="D80" s="31" t="n"/>
+      <c r="E80" s="31" t="n"/>
+      <c r="F80" s="31" t="n"/>
+    </row>
+    <row r="81" ht="15" customHeight="1">
+      <c r="A81" s="32" t="inlineStr">
+        <is>
+          <t>7999-9000</t>
+        </is>
+      </c>
+      <c r="B81" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL NET OPERATING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C81" s="34" t="n">
+        <v>12169.33</v>
+      </c>
+      <c r="D81" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="34" t="n">
+        <v>151153.1</v>
+      </c>
+      <c r="F81" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1">
+      <c r="A82" s="28" t="n"/>
+      <c r="B82" s="9" t="n"/>
+      <c r="C82" s="37" t="n"/>
+      <c r="D82" s="37" t="n"/>
+      <c r="E82" s="37" t="n"/>
+      <c r="F82" s="37" t="n"/>
+    </row>
+    <row r="83" ht="15" customHeight="1">
+      <c r="A83" s="38" t="inlineStr">
+        <is>
+          <t>7999-9999</t>
+        </is>
+      </c>
+      <c r="B83" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET OPERATING INCOME</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="n">
+        <v>20643.05</v>
+      </c>
+      <c r="D83" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="40" t="n">
+        <v>228968.36</v>
+      </c>
+      <c r="F83" s="40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="28" t="inlineStr">
+        <is>
+          <t>8170-0000</t>
+        </is>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Signage and Awnings</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="41" t="n">
+        <v>841.5700000000001</v>
+      </c>
+      <c r="F84" s="41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1">
+      <c r="A85" s="28" t="inlineStr">
+        <is>
+          <t>8179-9999</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Repairs Major</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>5385</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1">
+      <c r="A86" s="28" t="inlineStr">
+        <is>
+          <t>8389-9999</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Miscelleneous Non-Operating Expense</t>
+        </is>
+      </c>
+      <c r="C86" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="D86" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="29" t="n">
+        <v>15</v>
+      </c>
+      <c r="F86" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1">
+      <c r="A87" s="28" t="inlineStr">
+        <is>
+          <t>8390-0000</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL NON-RECURRING EXPENSES</t>
+        </is>
+      </c>
+      <c r="C87" s="30" t="n">
+        <v>15</v>
+      </c>
+      <c r="D87" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="30" t="n">
+        <v>6241.57</v>
+      </c>
+      <c r="F87" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1">
+      <c r="A88" s="28" t="inlineStr">
+        <is>
+          <t>8540-0000</t>
+        </is>
+      </c>
+      <c r="B88" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Loan Interest</t>
+        </is>
+      </c>
+      <c r="C88" s="29" t="n">
+        <v>8288.91</v>
+      </c>
+      <c r="D88" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="29" t="n">
+        <v>83770.84</v>
+      </c>
+      <c r="F88" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1">
+      <c r="A89" s="28" t="inlineStr">
+        <is>
+          <t>8590-0000</t>
+        </is>
+      </c>
+      <c r="B89" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            TOTAL LOAN INTEREST</t>
+        </is>
+      </c>
+      <c r="C89" s="30" t="n">
+        <v>8288.91</v>
+      </c>
+      <c r="D89" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="30" t="n">
+        <v>83770.84</v>
+      </c>
+      <c r="F89" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1">
+      <c r="A90" s="28" t="n"/>
+      <c r="B90" s="9" t="n"/>
+      <c r="C90" s="31" t="n"/>
+      <c r="D90" s="31" t="n"/>
+      <c r="E90" s="31" t="n"/>
+      <c r="F90" s="31" t="n"/>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="32" t="inlineStr">
+        <is>
+          <t>8990-0000</t>
+        </is>
+      </c>
+      <c r="B91" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                TOTAL EXPENSES</t>
+        </is>
+      </c>
+      <c r="C91" s="34" t="n">
+        <v>8303.91</v>
+      </c>
+      <c r="D91" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="34" t="n">
+        <v>90012.41</v>
+      </c>
+      <c r="F91" s="34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1">
+      <c r="A92" s="28" t="n"/>
+      <c r="B92" s="9" t="n"/>
+      <c r="C92" s="37" t="n"/>
+      <c r="D92" s="37" t="n"/>
+      <c r="E92" s="37" t="n"/>
+      <c r="F92" s="37" t="n"/>
+    </row>
+    <row r="93" ht="15" customHeight="1">
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>9090-0000</t>
+        </is>
+      </c>
+      <c r="B93" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    NET INCOME</t>
+        </is>
+      </c>
+      <c r="C93" s="42" t="n">
+        <v>12339.14</v>
+      </c>
+      <c r="D93" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="42" t="n">
+        <v>138955.95</v>
+      </c>
+      <c r="F93" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1">
+      <c r="A94" s="28" t="n"/>
+      <c r="B94" s="9" t="n"/>
+      <c r="C94" s="43" t="n"/>
+      <c r="D94" s="43" t="n"/>
+      <c r="E94" s="43" t="n"/>
+      <c r="F94" s="43" t="n"/>
+    </row>
+    <row r="95" ht="15" customHeight="1">
+      <c r="A95" s="28" t="n"/>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="n"/>
+      <c r="D95" s="18" t="n"/>
+      <c r="E95" s="18" t="n"/>
+      <c r="F95" s="18" t="n"/>
+    </row>
+    <row r="96" ht="15" customHeight="1">
+      <c r="A96" s="28" t="n"/>
+      <c r="B96" s="9" t="n"/>
+      <c r="C96" s="28" t="n"/>
+      <c r="D96" s="28" t="n"/>
+      <c r="E96" s="28" t="n"/>
+      <c r="F96" s="28" t="n"/>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="28" t="inlineStr">
+        <is>
+          <t>1300-0000</t>
+        </is>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="n">
+        <v>-2064.86</v>
+      </c>
+      <c r="D97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>-10322.33</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="28" t="inlineStr">
+        <is>
+          <t>1350-0001</t>
+        </is>
+      </c>
+      <c r="B98" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Pre-Paid Insurance</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="n">
+        <v>741.08</v>
+      </c>
+      <c r="D98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>-35.04</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="28" t="inlineStr">
+        <is>
+          <t>1910-0001</t>
+        </is>
+      </c>
+      <c r="B99" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Disputed Bank Transaction</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>-1516</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1">
+      <c r="A100" s="28" t="inlineStr">
+        <is>
+          <t>2110-0000</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Note 1 Principal</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="n">
+        <v>-2062.33</v>
+      </c>
+      <c r="D100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>-27213.04</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1">
+      <c r="A101" s="28" t="inlineStr">
+        <is>
+          <t>2150-0020</t>
+        </is>
+      </c>
+      <c r="B101" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Due To/(From) Other Property</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="n">
+        <v>25.45</v>
+      </c>
+      <c r="D101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>3104.97</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1">
+      <c r="A102" s="28" t="inlineStr">
+        <is>
+          <t>2200-0000</t>
+        </is>
+      </c>
+      <c r="B102" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Accounts Payable</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>-2457.91</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>3331.87</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1">
+      <c r="A103" s="28" t="inlineStr">
+        <is>
+          <t>2210-0000</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Prepaid Rent</t>
+        </is>
+      </c>
+      <c r="C103" s="29" t="n">
+        <v>-256.14</v>
+      </c>
+      <c r="D103" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="29" t="n">
+        <v>-509.92</v>
+      </c>
+      <c r="F103" s="29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1">
+      <c r="A104" s="28" t="inlineStr">
+        <is>
+          <t>2250-0000</t>
+        </is>
+      </c>
+      <c r="B104" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tenant Deposits</t>
+        </is>
+      </c>
+      <c r="C104" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="30" t="n">
+        <v>-940</v>
+      </c>
+      <c r="F104" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1">
+      <c r="A105" s="28" t="inlineStr">
+        <is>
+          <t>2270-0010</t>
+        </is>
+      </c>
+      <c r="B105" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Tenant Protection Net Payable</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" s="28" t="inlineStr">
+        <is>
+          <t>2305-0000</t>
+        </is>
+      </c>
+      <c r="B106" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Real Estate Tax Accrual</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="n">
+        <v>5024.87</v>
+      </c>
+      <c r="D106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>2206.68</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" s="28" t="inlineStr">
+        <is>
+          <t>2310-0000</t>
+        </is>
+      </c>
+      <c r="B107" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Sales Tax Collected</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="n">
+        <v>232.44</v>
+      </c>
+      <c r="D107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>1386.12</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" s="28" t="inlineStr">
+        <is>
+          <t>2640-0998</t>
+        </is>
+      </c>
+      <c r="B108" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Expense Accrual</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="n">
+        <v>552.23</v>
+      </c>
+      <c r="D108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>2340.91</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" ht="15" customHeight="1">
+      <c r="A109" s="28" t="inlineStr">
+        <is>
+          <t>2640-0999</t>
+        </is>
+      </c>
+      <c r="B109" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Payroll Accrual</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="n">
+        <v>54.95</v>
+      </c>
+      <c r="D109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>27.48</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" ht="15" customHeight="1">
+      <c r="A110" s="28" t="inlineStr">
+        <is>
+          <t>3300-0000</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Owner Distributions</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>-104335.19</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" ht="15" customHeight="1">
+      <c r="A111" s="28" t="n"/>
+      <c r="B111" s="9" t="n"/>
+      <c r="C111" s="31" t="n"/>
+      <c r="D111" s="31" t="n"/>
+      <c r="E111" s="31" t="n"/>
+      <c r="F111" s="31" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="28" t="n"/>
+      <c r="B112" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    TOTAL ADJUSTMENTS</t>
+        </is>
+      </c>
+      <c r="C112" s="30" t="n">
+        <v>-210.22</v>
+      </c>
+      <c r="D112" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="30" t="n">
+        <v>-132461.49</v>
+      </c>
+      <c r="F112" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="28" t="n"/>
+      <c r="B113" s="9" t="n"/>
+      <c r="C113" s="31" t="n"/>
+      <c r="D113" s="31" t="n"/>
+      <c r="E113" s="31" t="n"/>
+      <c r="F113" s="31" t="n"/>
+    </row>
+    <row r="114" ht="15" customHeight="1">
+      <c r="A114" s="28" t="n"/>
+      <c r="B114" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    CASH FLOW</t>
+        </is>
+      </c>
+      <c r="C114" s="30" t="n">
+        <v>12128.92</v>
+      </c>
+      <c r="D114" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="30" t="n">
+        <v>6494.46</v>
+      </c>
+      <c r="F114" s="30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" ht="15" customHeight="1">
+      <c r="A115" s="28" t="n"/>
+    </row>
+    <row r="116" ht="15" customHeight="1">
+      <c r="A116" s="28" t="n"/>
+      <c r="B116" s="33" t="inlineStr">
+        <is>
+          <t>Period to Date</t>
+        </is>
+      </c>
+      <c r="C116" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D116" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E116" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F116" s="28" t="n"/>
+    </row>
+    <row r="117" ht="15" customHeight="1">
+      <c r="A117" s="28" t="inlineStr">
+        <is>
+          <t>1110-4974</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Crystal Lake</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>16045.13</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>28174.05</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>12128.92</v>
+      </c>
+      <c r="F117" s="28" t="n"/>
+    </row>
+    <row r="118" ht="15" customHeight="1">
+      <c r="A118" s="28" t="n"/>
+      <c r="B118" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C118" s="44" t="n">
+        <v>16045.13</v>
+      </c>
+      <c r="D118" s="44" t="n">
+        <v>28174.05</v>
+      </c>
+      <c r="E118" s="44" t="n">
+        <v>12128.92</v>
+      </c>
+      <c r="F118" s="28" t="n"/>
+    </row>
+    <row r="119" ht="15" customHeight="1">
+      <c r="A119" s="28" t="n"/>
+    </row>
+    <row r="120" ht="15" customHeight="1">
+      <c r="A120" s="28" t="n"/>
+      <c r="B120" s="33" t="inlineStr">
+        <is>
+          <t>Year to Date</t>
+        </is>
+      </c>
+      <c r="C120" s="32" t="inlineStr">
+        <is>
+          <t>Beginning Balance</t>
+        </is>
+      </c>
+      <c r="D120" s="32" t="inlineStr">
+        <is>
+          <t>Ending Balance</t>
+        </is>
+      </c>
+      <c r="E120" s="32" t="inlineStr">
+        <is>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="F120" s="28" t="n"/>
+    </row>
+    <row r="121" ht="15" customHeight="1">
+      <c r="A121" s="28" t="inlineStr">
+        <is>
+          <t>1110-4974</t>
+        </is>
+      </c>
+      <c r="B121" s="9" t="inlineStr">
+        <is>
+          <t>Storsafe Management Solutions - Crystal Lake</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="n">
+        <v>21679.59</v>
+      </c>
+      <c r="D121" s="12" t="n">
+        <v>28174.05</v>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>6494.46</v>
+      </c>
+      <c r="F121" s="28" t="n"/>
+    </row>
+    <row r="122" ht="15" customHeight="1">
+      <c r="A122" s="28" t="n"/>
+      <c r="B122" s="33" t="inlineStr">
+        <is>
+          <t>Total Cash</t>
+        </is>
+      </c>
+      <c r="C122" s="44" t="n">
+        <v>21679.59</v>
+      </c>
+      <c r="D122" s="44" t="n">
+        <v>28174.05</v>
+      </c>
+      <c r="E122" s="44" t="n">
+        <v>6494.46</v>
+      </c>
+      <c r="F122" s="28" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>